--- a/food_beverage_order_forms/021_farm_egg_and_dairy_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/021_farm_egg_and_dairy_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,9 +440,9 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_1</t>
+          <t>customer_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Farm Egg and Dairy Order Form</t>
+          <t>Customer Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,35 +543,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_2</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Customer Information</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_3</t>
+          <t>order_items_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Select Items 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_4</t>
+          <t>order_items_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Order Information</t>
+          <t>Select Items 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_5</t>
+          <t>order_items_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Order Information</t>
+          <t>Select Items 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,86 +630,86 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_6</t>
+          <t>order_description</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Order Information</t>
+          <t>Order Description</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_7</t>
+          <t>delivery_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Order Information</t>
+          <t>Delivery Date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_8</t>
+          <t>delivery_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Order Information</t>
+          <t>Delivery Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_9</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Order Information</t>
+          <t>Payment Method</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,40 +722,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_10</t>
+          <t>order_total</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Order Information</t>
+          <t>Order Total</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_11</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -776,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,357 +804,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_4_choices</t>
+          <t>order_items_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_4_choices</t>
+          <t>order_items_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>banana</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Banana</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_4_choices</t>
+          <t>order_items_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_5_choices</t>
+          <t>order_items_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_5_choices</t>
+          <t>order_items_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>banana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Banana</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_5_choices</t>
+          <t>order_items_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_6_choices</t>
+          <t>order_items_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_6_choices</t>
+          <t>order_items_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>banana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Banana</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_6_choices</t>
+          <t>order_items_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_7_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_7_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>farm_egg_and_dairy_order_form_page_7_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>debit_card</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>farm_egg_and_dairy_order_form_page_8_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>item_1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>farm_egg_and_dairy_order_form_page_8_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>item_2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>farm_egg_and_dairy_order_form_page_8_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>item_3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>farm_egg_and_dairy_order_form_page_9_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>item_1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>farm_egg_and_dairy_order_form_page_9_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>item_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>farm_egg_and_dairy_order_form_page_9_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>item_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>farm_egg_and_dairy_order_form_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>item_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>farm_egg_and_dairy_order_form_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>item_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>farm_egg_and_dairy_order_form_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>item_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Item 3</t>
+          <t>Debit Card</t>
         </is>
       </c>
     </row>
